--- a/output/План лекций курса системного аналитика.updated.xlsx
+++ b/output/План лекций курса системного аналитика.updated.xlsx
@@ -411,7 +411,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Готово: 41 из 98. Перегенерированы 14–17 (REQ-STAKEHOLDERS … REQ-SPECIFICATION). Осталось needs_revision: 5. Следующая: 18. REQ-MANAGEMENT.</v>
+        <v>Готово: 42 из 98. Перегенерированы 14–18 (до REQ-MANAGEMENT). Осталось needs_revision: 4. Следующая: 19. UML-USE-CASE.</v>
       </c>
     </row>
     <row r="4">
@@ -1112,19 +1112,19 @@
 - * Управление требованиями</v>
       </c>
       <c r="B22" t="str">
-        <v>Нет</v>
+        <v>Да</v>
       </c>
       <c r="C22" t="str">
-        <v>Нет</v>
+        <v>Да</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>Лекция: lecture.md\nПрактика: exercises.md\nОтветы: answers.md\nSources: sources.md</v>
       </c>
       <c r="E22" t="str">
-        <v>Утерян после re-clone (не попал в git); нужна перегенерация</v>
+        <v>Урок без новых canonical expected_artifacts. Управление требованиями — процессный урок.</v>
       </c>
       <c r="F22" t="str">
-        <v>Нужна перегенерация</v>
+        <v>Готово</v>
       </c>
       <c r="G22">
         <v>18</v>
@@ -1133,10 +1133,10 @@
         <v>REQ-MANAGEMENT</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>output/M03/REQ-MANAGEMENT/</v>
       </c>
       <c r="J22" t="str">
-        <v>manual-20260813-REQ-MANAGEMENT</v>
+        <v>20261018T183322Z_REQ-MANAGEMENT_bb789b</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
